--- a/lorenzo-playwright-kdf/excelFramework/testcases/CaseLoad/LSTP_CaseLoad_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/CaseLoad/LSTP_CaseLoad_WF001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smani57\ORBIS PAS UKI-LZO 1\ORBIS PAS UKI-LZO\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\CaseLoad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\CaseLoad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768C63E9-E1C4-40D1-81F8-2D0081AF578A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427D9B89-90B0-4282-A2B5-CBB674BA1EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45C6BE27-5324-4041-A113-6D22C593EB70}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{45C6BE27-5324-4041-A113-6D22C593EB70}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -1762,7 +1762,7 @@
         <v>93</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>94</v>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/CaseLoad/LSTP_CaseLoad_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/CaseLoad/LSTP_CaseLoad_WF001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\CaseLoad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427D9B89-90B0-4282-A2B5-CBB674BA1EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F780E604-2472-4302-A1D0-1C43ADE214D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{45C6BE27-5324-4041-A113-6D22C593EB70}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{45C6BE27-5324-4041-A113-6D22C593EB70}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="381">
   <si>
     <t>StepNo</t>
   </si>
@@ -1182,6 +1182,9 @@
   </si>
   <si>
     <t>Discharged</t>
+  </si>
+  <si>
+    <t>launchRegistration</t>
   </si>
 </sst>
 </file>
@@ -2231,7 +2234,7 @@
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="8" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -2357,7 +2360,7 @@
         <v>89</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>89</v>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/CaseLoad/LSTP_CaseLoad_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/CaseLoad/LSTP_CaseLoad_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\CaseLoad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F780E604-2472-4302-A1D0-1C43ADE214D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61F4D62-B7F7-4A22-B3F8-D53FAF5FE9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{45C6BE27-5324-4041-A113-6D22C593EB70}"/>
   </bookViews>
@@ -1028,9 +1028,6 @@
     <t>Click In-tray from context sub-task pane to access transfer notification</t>
   </si>
   <si>
-    <t>lnkSubTaskPaneIn-tray</t>
-  </si>
-  <si>
     <t>Wait for In-tray page to load</t>
   </si>
   <si>
@@ -1185,6 +1182,9 @@
   </si>
   <si>
     <t>launchRegistration</t>
+  </si>
+  <si>
+    <t>lnkSubTaskPaneInTray</t>
   </si>
 </sst>
 </file>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -2360,7 +2360,7 @@
         <v>89</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>89</v>
@@ -2639,31 +2639,31 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D31" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J31" s="5" t="s">
         <v>356</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>357</v>
       </c>
       <c r="K31" s="5"/>
     </row>
@@ -2705,7 +2705,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>12</v>
@@ -2717,19 +2717,19 @@
         <v>89</v>
       </c>
       <c r="F33" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J33" s="5" t="s">
         <v>359</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>360</v>
       </c>
       <c r="K33" s="5"/>
     </row>
@@ -3541,13 +3541,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E67" s="10"/>
       <c r="F67" s="10" t="s">
@@ -3564,13 +3564,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E68" s="10"/>
       <c r="F68" s="10" t="s">
@@ -3587,13 +3587,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E69" s="10"/>
       <c r="F69" s="10" t="s">
@@ -3635,7 +3635,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>12</v>
@@ -3684,7 +3684,7 @@
         <v>213</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D73" s="10"/>
       <c r="E73" s="10"/>
@@ -3702,10 +3702,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="C74" s="10" t="s">
         <v>346</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>347</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>214</v>
@@ -3730,7 +3730,7 @@
         <v>215</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D75" s="10"/>
       <c r="E75" s="10"/>
@@ -3751,7 +3751,7 @@
         <v>216</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>217</v>
@@ -3771,7 +3771,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="10" t="s">
@@ -3781,19 +3781,19 @@
         <v>89</v>
       </c>
       <c r="F77" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="I77" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="J77" s="10" t="s">
         <v>363</v>
-      </c>
-      <c r="G77" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="I77" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="J77" s="10" t="s">
-        <v>364</v>
       </c>
       <c r="K77" s="10"/>
     </row>
@@ -3802,13 +3802,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>89</v>
@@ -3833,13 +3833,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>89</v>
@@ -3857,7 +3857,7 @@
         <v>89</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K79" s="10"/>
     </row>
@@ -3866,7 +3866,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C80" s="10" t="s">
         <v>12</v>
@@ -3897,10 +3897,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>113</v>
@@ -3923,7 +3923,7 @@
         <v>218</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D82" s="10"/>
       <c r="E82" s="10"/>
@@ -3949,13 +3949,13 @@
       <c r="D83" s="10"/>
       <c r="E83" s="10"/>
       <c r="F83" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G83" s="10"/>
       <c r="H83" s="10"/>
       <c r="I83" s="10"/>
       <c r="J83" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K83" s="10"/>
     </row>
@@ -3967,7 +3967,7 @@
         <v>218</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D84" s="10"/>
       <c r="E84" s="10"/>
@@ -3990,7 +3990,7 @@
         <v>220</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D85" s="10" t="s">
         <v>221</v>
@@ -4010,10 +4010,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>223</v>
@@ -4033,10 +4033,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>289</v>
@@ -4059,7 +4059,7 @@
         <v>224</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>20</v>
@@ -4082,7 +4082,7 @@
         <v>225</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>226</v>
@@ -4105,7 +4105,7 @@
         <v>229</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D90" s="10" t="s">
         <v>230</v>
@@ -4118,7 +4118,7 @@
       <c r="H90" s="10"/>
       <c r="I90" s="10"/>
       <c r="J90" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K90" s="10" t="s">
         <v>22</v>
@@ -4132,7 +4132,7 @@
         <v>231</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>232</v>
@@ -4155,7 +4155,7 @@
         <v>222</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>223</v>
@@ -4178,7 +4178,7 @@
         <v>233</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>23</v>
@@ -4201,7 +4201,7 @@
         <v>234</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D94" s="10"/>
       <c r="E94" s="10"/>
@@ -4219,10 +4219,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>289</v>
@@ -4327,13 +4327,13 @@
       <c r="D99" s="10"/>
       <c r="E99" s="10"/>
       <c r="F99" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G99" s="10"/>
       <c r="H99" s="10"/>
       <c r="I99" s="10"/>
       <c r="J99" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K99" s="10"/>
     </row>
@@ -4427,7 +4427,7 @@
       <c r="H103" s="10"/>
       <c r="I103" s="10"/>
       <c r="J103" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="K103" s="10" t="s">
         <v>25</v>
@@ -4567,13 +4567,13 @@
       <c r="D109" s="10"/>
       <c r="E109" s="10"/>
       <c r="F109" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G109" s="10"/>
       <c r="H109" s="10"/>
       <c r="I109" s="10"/>
       <c r="J109" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K109" s="10"/>
     </row>
@@ -4665,7 +4665,7 @@
       <c r="H113" s="10"/>
       <c r="I113" s="10"/>
       <c r="J113" s="10" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="K113" s="10" t="s">
         <v>26</v>
@@ -4828,13 +4828,13 @@
       <c r="D120" s="10"/>
       <c r="E120" s="10"/>
       <c r="F120" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G120" s="10"/>
       <c r="H120" s="10"/>
       <c r="I120" s="10"/>
       <c r="J120" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K120" s="10"/>
     </row>
@@ -4926,7 +4926,7 @@
       <c r="H124" s="10"/>
       <c r="I124" s="10"/>
       <c r="J124" s="10" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="K124" s="10" t="s">
         <v>27</v>
@@ -5110,13 +5110,13 @@
       <c r="D132" s="10"/>
       <c r="E132" s="10"/>
       <c r="F132" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G132" s="10"/>
       <c r="H132" s="10"/>
       <c r="I132" s="10"/>
       <c r="J132" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K132" s="10"/>
     </row>
@@ -5208,7 +5208,7 @@
       <c r="H136" s="10"/>
       <c r="I136" s="10"/>
       <c r="J136" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="K136" s="10" t="s">
         <v>28</v>
@@ -5430,13 +5430,13 @@
       <c r="D146" s="10"/>
       <c r="E146" s="10"/>
       <c r="F146" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G146" s="10"/>
       <c r="H146" s="10"/>
       <c r="I146" s="10"/>
       <c r="J146" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K146" s="10"/>
     </row>
@@ -5643,13 +5643,13 @@
       <c r="D155" s="10"/>
       <c r="E155" s="10"/>
       <c r="F155" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G155" s="10"/>
       <c r="H155" s="10"/>
       <c r="I155" s="10"/>
       <c r="J155" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K155" s="10"/>
     </row>
@@ -6022,7 +6022,7 @@
         <v>205</v>
       </c>
       <c r="D172" s="10" t="s">
-        <v>328</v>
+        <v>380</v>
       </c>
       <c r="E172" s="10"/>
       <c r="F172" s="10" t="s">
@@ -6039,10 +6039,10 @@
         <v>172</v>
       </c>
       <c r="B173" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="C173" s="10" t="s">
         <v>329</v>
-      </c>
-      <c r="C173" s="10" t="s">
-        <v>330</v>
       </c>
       <c r="D173" s="10"/>
       <c r="E173" s="10"/>
@@ -6060,13 +6060,13 @@
         <v>173</v>
       </c>
       <c r="B174" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="C174" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D174" s="10" t="s">
         <v>331</v>
-      </c>
-      <c r="C174" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="D174" s="10" t="s">
-        <v>332</v>
       </c>
       <c r="E174" s="10"/>
       <c r="F174" s="10" t="s">
@@ -6083,10 +6083,10 @@
         <v>174</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D175" s="10"/>
       <c r="E175" s="10"/>
@@ -6104,13 +6104,13 @@
         <v>175</v>
       </c>
       <c r="B176" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="C176" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D176" s="10" t="s">
         <v>334</v>
-      </c>
-      <c r="C176" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="D176" s="10" t="s">
-        <v>335</v>
       </c>
       <c r="E176" s="10"/>
       <c r="F176" s="10" t="s">
@@ -6129,10 +6129,10 @@
         <v>176</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C177" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D177" s="10" t="s">
         <v>258</v>
@@ -6152,7 +6152,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C178" s="10" t="s">
         <v>205</v>
@@ -6173,7 +6173,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C179" s="10" t="s">
         <v>205</v>
@@ -6202,7 +6202,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C180" s="10" t="s">
         <v>205</v>
@@ -6231,13 +6231,13 @@
         <v>180</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C181" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D181" s="10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E181" s="10"/>
       <c r="F181" s="10" t="s">
@@ -6254,13 +6254,13 @@
         <v>181</v>
       </c>
       <c r="B182" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C182" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D182" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E182" s="10"/>
       <c r="F182" s="10" t="s">
@@ -6277,7 +6277,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="10"/>
@@ -6340,7 +6340,7 @@
         <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D2" t="s">
         <v>38</v>
@@ -6354,7 +6354,7 @@
         <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D3" t="s">
         <v>40</v>
@@ -6368,7 +6368,7 @@
         <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D4" t="s">
         <v>42</v>
@@ -6382,7 +6382,7 @@
         <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D5" t="s">
         <v>44</v>
@@ -6679,7 +6679,7 @@
         <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
